--- a/data/trans_orig/P1203-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1203-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de sentirse desanimado y triste en 2007</t>
+          <t>Población según frecuencia de sentirse desanimado y triste en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>388951</t>
+          <t>388043</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>449737</t>
+          <t>451908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>406919</t>
+          <t>405740</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>473393</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>811706</t>
+          <t>813511</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>902517</t>
+          <t>901347</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251334</t>
+          <t>250892</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308188</t>
+          <t>308640</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>326916</t>
+          <t>329517</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389512</t>
+          <t>397513</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>596296</t>
+          <t>597772</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>217103</t>
+          <t>216453</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>271622</t>
+          <t>269741</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>329183</t>
+          <t>328281</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>395027</t>
+          <t>393642</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>562085</t>
+          <t>562818</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>645604</t>
+          <t>644913</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54622</t>
+          <t>55625</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86212</t>
+          <t>89109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85179</t>
+          <t>85250</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123684</t>
+          <t>126664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>149442</t>
+          <t>147589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>199073</t>
+          <t>196990</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24967</t>
+          <t>24431</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17049</t>
+          <t>17519</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38465</t>
+          <t>36424</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30360</t>
+          <t>29925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56304</t>
+          <t>55399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15924</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13445</t>
+          <t>14200</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32028</t>
+          <t>34426</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20382</t>
+          <t>20792</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>44252</t>
+          <t>43426</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1042168</t>
+          <t>1040759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1120095</t>
+          <t>1119158</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>772673</t>
+          <t>772436</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>850857</t>
+          <t>851674</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1838250</t>
+          <t>1838775</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1950670</t>
+          <t>1947918</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>332004</t>
+          <t>331110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>397315</t>
+          <t>398482</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>359244</t>
+          <t>354257</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>422870</t>
+          <t>423209</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>705350</t>
+          <t>705529</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>804576</t>
+          <t>799432</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>166791</t>
+          <t>164243</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>218514</t>
+          <t>217980</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>256572</t>
+          <t>253796</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>316659</t>
+          <t>317372</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>435602</t>
+          <t>433910</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>512790</t>
+          <t>514535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>28134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54550</t>
+          <t>54049</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47450</t>
+          <t>47340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75678</t>
+          <t>77661</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83005</t>
+          <t>80958</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123155</t>
+          <t>119391</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20627</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13797</t>
+          <t>14190</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32452</t>
+          <t>33565</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23823</t>
+          <t>23291</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>48052</t>
+          <t>47262</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11032</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29786</t>
+          <t>31336</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17049</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38537</t>
+          <t>38242</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>313995</t>
+          <t>313544</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>360978</t>
+          <t>361728</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>226680</t>
+          <t>227404</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>274221</t>
+          <t>271149</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>554261</t>
+          <t>554592</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>620758</t>
+          <t>621916</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,51%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116469</t>
+          <t>114628</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>157951</t>
+          <t>155175</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88901</t>
+          <t>90384</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>125807</t>
+          <t>128385</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>210836</t>
+          <t>212745</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>270119</t>
+          <t>269449</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50803</t>
+          <t>50335</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81528</t>
+          <t>81855</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72192</t>
+          <t>71888</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>105884</t>
+          <t>106954</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>131390</t>
+          <t>132019</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>179247</t>
+          <t>178533</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24335</t>
+          <t>24181</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>35124</t>
+          <t>33583</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12949</t>
+          <t>13549</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19109</t>
+          <t>19278</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>9031</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27062</t>
+          <t>27446</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12220</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>15028</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1777496</t>
+          <t>1775778</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1902139</t>
+          <t>1893391</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1446440</t>
+          <t>1439781</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1565490</t>
+          <t>1558026</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3258566</t>
+          <t>3259736</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3426644</t>
+          <t>3418525</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>729078</t>
+          <t>730931</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>827195</t>
+          <t>826305</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>807832</t>
+          <t>805306</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>912502</t>
+          <t>907730</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1566256</t>
+          <t>1560079</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1702396</t>
+          <t>1704275</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>457565</t>
+          <t>458331</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>538602</t>
+          <t>540597</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>684152</t>
+          <t>689229</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>779676</t>
+          <t>789759</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1172080</t>
+          <t>1169856</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1299901</t>
+          <t>1294474</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>97388</t>
+          <t>94977</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>139975</t>
+          <t>137997</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>154720</t>
+          <t>156976</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>206323</t>
+          <t>208110</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>262515</t>
+          <t>263469</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>327866</t>
+          <t>325748</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22790</t>
+          <t>21930</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46701</t>
+          <t>45855</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>45362</t>
+          <t>45544</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>75406</t>
+          <t>76331</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>75381</t>
+          <t>73704</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>113383</t>
+          <t>111470</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25854</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>35460</t>
+          <t>34341</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>63579</t>
+          <t>64918</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>50868</t>
+          <t>48627</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>83393</t>
+          <t>82887</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de sentirse desanimado y triste en 2012</t>
+          <t>Población según frecuencia de sentirse desanimado y triste en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>276042</t>
+          <t>277085</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>335170</t>
+          <t>333707</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>275267</t>
+          <t>274632</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>341445</t>
+          <t>340464</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>564494</t>
+          <t>568705</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>653819</t>
+          <t>661129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276032</t>
+          <t>274617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>334016</t>
+          <t>335240</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>341406</t>
+          <t>341409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>409120</t>
+          <t>407617</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>636627</t>
+          <t>634808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>729335</t>
+          <t>724130</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>201132</t>
+          <t>201274</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>257141</t>
+          <t>257427</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>371036</t>
+          <t>368970</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>436952</t>
+          <t>437679</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>591786</t>
+          <t>589654</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>679698</t>
+          <t>676104</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53940</t>
+          <t>53006</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86711</t>
+          <t>86525</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>113283</t>
+          <t>116167</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>158749</t>
+          <t>161062</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179459</t>
+          <t>178199</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>233631</t>
+          <t>234122</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34049</t>
+          <t>33290</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62317</t>
+          <t>61894</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56695</t>
+          <t>55554</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90248</t>
+          <t>88905</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98726</t>
+          <t>97227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142729</t>
+          <t>141349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32128</t>
+          <t>30612</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31761</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57594</t>
+          <t>59559</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48233</t>
+          <t>49368</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>81574</t>
+          <t>81829</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>892684</t>
+          <t>894999</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>983561</t>
+          <t>980599</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>617884</t>
+          <t>621505</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>704830</t>
+          <t>708571</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1543877</t>
+          <t>1538544</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1664441</t>
+          <t>1671411</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,99%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>506006</t>
+          <t>509190</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>587920</t>
+          <t>591952</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>456117</t>
+          <t>452791</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>531690</t>
+          <t>530203</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>982066</t>
+          <t>987820</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1098510</t>
+          <t>1101045</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>316680</t>
+          <t>317890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>386787</t>
+          <t>385717</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>372365</t>
+          <t>367401</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>444280</t>
+          <t>443696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>706141</t>
+          <t>706297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>806588</t>
+          <t>807209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58110</t>
+          <t>57035</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89800</t>
+          <t>92826</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73399</t>
+          <t>75266</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>113265</t>
+          <t>114412</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>139610</t>
+          <t>139922</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>191036</t>
+          <t>192353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>25727</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53413</t>
+          <t>53426</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51538</t>
+          <t>53497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>86410</t>
+          <t>87079</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>86626</t>
+          <t>85513</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>129706</t>
+          <t>127719</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20152</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42488</t>
+          <t>41963</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30982</t>
+          <t>31012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56019</t>
+          <t>57486</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>221480</t>
+          <t>222715</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>268016</t>
+          <t>266855</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>169698</t>
+          <t>169420</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>213915</t>
+          <t>215889</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>404078</t>
+          <t>404607</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>468222</t>
+          <t>468611</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,97%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>128920</t>
+          <t>131259</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>174202</t>
+          <t>173395</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>129088</t>
+          <t>129043</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>173845</t>
+          <t>171403</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>272126</t>
+          <t>274706</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>334475</t>
+          <t>333904</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53261</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>86898</t>
+          <t>86749</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70359</t>
+          <t>68602</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>105561</t>
+          <t>103801</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>130166</t>
+          <t>131447</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>179908</t>
+          <t>178761</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21442</t>
+          <t>22354</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25247</t>
+          <t>25522</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15982</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>41540</t>
+          <t>39272</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11208</t>
+          <t>11574</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25607</t>
+          <t>24555</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10696</t>
+          <t>9971</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31108</t>
+          <t>31606</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6334,62 +6334,62 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>5663</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>5017</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1425330</t>
+          <t>1431466</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1546096</t>
+          <t>1550622</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1108580</t>
+          <t>1099926</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1222399</t>
+          <t>1214254</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2566995</t>
+          <t>2573573</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2739098</t>
+          <t>2735004</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>948643</t>
+          <t>951912</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1059853</t>
+          <t>1058516</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>962143</t>
+          <t>967806</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1078234</t>
+          <t>1078416</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1946461</t>
+          <t>1942953</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2100813</t>
+          <t>2105724</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>599524</t>
+          <t>597121</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>692544</t>
+          <t>694742</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>841397</t>
+          <t>844265</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>951820</t>
+          <t>951940</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1470368</t>
+          <t>1470620</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1611841</t>
+          <t>1614476</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>129793</t>
+          <t>127647</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178528</t>
+          <t>177859</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>213503</t>
+          <t>214725</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>274505</t>
+          <t>277316</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>357678</t>
+          <t>359287</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>441805</t>
+          <t>439846</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>69780</t>
+          <t>70424</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>109670</t>
+          <t>110790</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>130319</t>
+          <t>129303</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>181164</t>
+          <t>180923</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>212683</t>
+          <t>211673</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>277326</t>
+          <t>276762</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22987</t>
+          <t>22648</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46992</t>
+          <t>47079</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>55959</t>
+          <t>56786</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>90151</t>
+          <t>93339</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>86019</t>
+          <t>87584</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>129189</t>
+          <t>131028</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7360,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de sentirse desanimado y triste en 2016</t>
+          <t>Población según frecuencia de sentirse desanimado y triste en 2016 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>203210</t>
+          <t>202146</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>253639</t>
+          <t>252088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>188368</t>
+          <t>186849</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>241003</t>
+          <t>241062</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>404676</t>
+          <t>402346</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>483261</t>
+          <t>476396</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>200516</t>
+          <t>197314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>247638</t>
+          <t>246833</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239351</t>
+          <t>239059</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297073</t>
+          <t>297351</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>451623</t>
+          <t>450155</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>529841</t>
+          <t>527822</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -7781,12 +7781,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>180149</t>
+          <t>180671</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>227210</t>
+          <t>227538</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>268653</t>
+          <t>269976</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>328979</t>
+          <t>330231</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>466262</t>
+          <t>460979</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>542886</t>
+          <t>543041</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46100</t>
+          <t>46617</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75490</t>
+          <t>75278</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88577</t>
+          <t>87965</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>130429</t>
+          <t>127688</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142965</t>
+          <t>142386</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>192180</t>
+          <t>191716</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17307</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37801</t>
+          <t>37892</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54465</t>
+          <t>53130</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87382</t>
+          <t>87419</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76881</t>
+          <t>76641</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>114526</t>
+          <t>116662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8376</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23791</t>
+          <t>24051</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25550</t>
+          <t>25679</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49740</t>
+          <t>51710</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>37669</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>67451</t>
+          <t>67749</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>827879</t>
+          <t>827153</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>919968</t>
+          <t>921967</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>660493</t>
+          <t>658338</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>743858</t>
+          <t>745716</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1518149</t>
+          <t>1507894</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1637602</t>
+          <t>1643599</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -8463,12 +8463,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>656603</t>
+          <t>657497</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>747355</t>
+          <t>742294</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>617802</t>
+          <t>618248</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>700009</t>
+          <t>702318</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1295877</t>
+          <t>1294161</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1425161</t>
+          <t>1422103</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>340942</t>
+          <t>344124</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>412800</t>
+          <t>413078</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>410436</t>
+          <t>412108</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>487379</t>
+          <t>485533</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>773587</t>
+          <t>773513</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>885182</t>
+          <t>882989</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50004</t>
+          <t>49388</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81252</t>
+          <t>82966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78755</t>
+          <t>80131</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>121262</t>
+          <t>120254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>140326</t>
+          <t>140991</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>190038</t>
+          <t>192957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17699</t>
+          <t>17265</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39026</t>
+          <t>38289</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39628</t>
+          <t>39020</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70626</t>
+          <t>68373</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>63329</t>
+          <t>62257</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>97870</t>
+          <t>98186</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -8915,12 +8915,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41559</t>
+          <t>42044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>15818</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38098</t>
+          <t>36380</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38890</t>
+          <t>39862</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70842</t>
+          <t>68779</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9000,12 +9000,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>230948</t>
+          <t>231323</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>280580</t>
+          <t>278756</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9160,12 +9160,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>195738</t>
+          <t>193389</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>241877</t>
+          <t>239410</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>438049</t>
+          <t>441952</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>507837</t>
+          <t>508733</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -9258,12 +9258,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>159735</t>
+          <t>157243</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>204499</t>
+          <t>204320</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>172559</t>
+          <t>174321</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>217418</t>
+          <t>218608</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>343622</t>
+          <t>346870</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>409304</t>
+          <t>409573</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,41%</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64833</t>
+          <t>64972</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>100330</t>
+          <t>101355</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>94757</t>
+          <t>95299</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>132665</t>
+          <t>133521</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>168169</t>
+          <t>170200</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>219649</t>
+          <t>222268</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28897</t>
+          <t>29234</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5783</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20581</t>
+          <t>21110</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18362</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>41940</t>
+          <t>43210</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>14720</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>14546</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22919</t>
+          <t>21951</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9725,47 +9725,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>4976</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>11834</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>4976</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>1922</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>10873</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17627</t>
+          <t>18194</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -9940,12 +9940,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1296029</t>
+          <t>1294187</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1417992</t>
+          <t>1414321</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1075464</t>
+          <t>1077794</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1190021</t>
+          <t>1186028</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9990,12 +9990,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2405471</t>
+          <t>2408390</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2568810</t>
+          <t>2558235</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,09%</t>
         </is>
       </c>
     </row>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1052712</t>
+          <t>1053044</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1166578</t>
+          <t>1162536</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1062982</t>
+          <t>1065818</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1176115</t>
+          <t>1181744</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2152275</t>
+          <t>2148587</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2312768</t>
+          <t>2301504</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>615259</t>
+          <t>620044</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>711690</t>
+          <t>714419</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10181,82 +10181,82 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
+          <t>21,18%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>860007</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>808393</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>913163</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>22,93%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>25,91%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>1521343</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>1455015</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>1589357</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>22,06%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
           <t>21,1%</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>801</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>860007</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>809944</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>911829</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>22,98%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>25,87%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>1428</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>1521343</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>1451149</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>1594024</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>22,06%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>21,04%</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>118952</t>
+          <t>120627</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>167350</t>
+          <t>166529</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>189118</t>
+          <t>188441</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>248213</t>
+          <t>247369</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>322355</t>
+          <t>317735</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>399716</t>
+          <t>399597</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44506</t>
+          <t>45175</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>75702</t>
+          <t>75723</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>108308</t>
+          <t>105919</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>156796</t>
+          <t>151626</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>160441</t>
+          <t>160601</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>215213</t>
+          <t>215586</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -10505,12 +10505,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>35715</t>
+          <t>35581</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63691</t>
+          <t>63923</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10540,12 +10540,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>50078</t>
+          <t>51172</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>84816</t>
+          <t>84551</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>95489</t>
+          <t>95774</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>140549</t>
+          <t>140322</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -10771,7 +10771,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de sentirse desanimado y triste en 2023</t>
+          <t>Población según frecuencia de sentirse desanimado y triste en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10966,12 +10966,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>162395</t>
+          <t>164546</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>203184</t>
+          <t>204435</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10981,12 +10981,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>144356</t>
+          <t>145167</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>180802</t>
+          <t>181228</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>318082</t>
+          <t>320041</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>374791</t>
+          <t>375395</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -11079,12 +11079,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92044</t>
+          <t>92024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>124178</t>
+          <t>125595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>154150</t>
+          <t>152771</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>189488</t>
+          <t>186594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>253305</t>
+          <t>253526</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>302392</t>
+          <t>301957</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11164,12 +11164,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -11192,12 +11192,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114663</t>
+          <t>113547</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>150180</t>
+          <t>149688</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11207,12 +11207,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>215953</t>
+          <t>214192</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>253922</t>
+          <t>257159</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11242,12 +11242,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>338805</t>
+          <t>340530</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>393803</t>
+          <t>395456</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11277,12 +11277,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -11305,12 +11305,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34211</t>
+          <t>34297</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56816</t>
+          <t>56166</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84688</t>
+          <t>85464</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112633</t>
+          <t>111383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>125561</t>
+          <t>125111</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>160905</t>
+          <t>160827</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11390,12 +11390,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -11418,12 +11418,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21108</t>
+          <t>20053</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41427</t>
+          <t>39731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11453,12 +11453,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53051</t>
+          <t>53432</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79118</t>
+          <t>77946</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11468,12 +11468,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11488,12 +11488,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>80338</t>
+          <t>78476</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110836</t>
+          <t>111219</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11503,12 +11503,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11734</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28795</t>
+          <t>27870</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18475</t>
+          <t>19192</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33790</t>
+          <t>33344</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11601,12 +11601,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35619</t>
+          <t>35363</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>55337</t>
+          <t>56663</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11616,12 +11616,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -11761,12 +11761,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>689867</t>
+          <t>662706</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1128266</t>
+          <t>1123807</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>567317</t>
+          <t>600802</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>931036</t>
+          <t>934657</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11811,12 +11811,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1433831</t>
+          <t>1437896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2007140</t>
+          <t>2025883</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11846,12 +11846,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,78%</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>362871</t>
+          <t>361026</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>590115</t>
+          <t>597365</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11909,12 +11909,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>344198</t>
+          <t>368119</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>566911</t>
+          <t>564753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11924,12 +11924,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11944,12 +11944,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>826013</t>
+          <t>809017</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1129642</t>
+          <t>1128892</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11959,12 +11959,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -11987,12 +11987,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>377113</t>
+          <t>377536</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1095623</t>
+          <t>1130126</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>487022</t>
+          <t>484127</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1167041</t>
+          <t>1102413</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>938519</t>
+          <t>914677</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1879002</t>
+          <t>1942511</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -12100,12 +12100,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68316</t>
+          <t>71615</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128138</t>
+          <t>127826</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12115,12 +12115,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12135,12 +12135,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95394</t>
+          <t>96496</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154438</t>
+          <t>154601</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12150,7 +12150,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -12170,12 +12170,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>185737</t>
+          <t>186333</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>268536</t>
+          <t>270488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12185,12 +12185,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -12213,12 +12213,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34901</t>
+          <t>34885</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>75077</t>
+          <t>75497</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12248,12 +12248,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52225</t>
+          <t>54006</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91662</t>
+          <t>93538</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12263,12 +12263,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12283,12 +12283,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>100802</t>
+          <t>101057</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>155588</t>
+          <t>155233</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20333</t>
+          <t>20518</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46753</t>
+          <t>47449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48702</t>
+          <t>49934</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52018</t>
+          <t>50483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89670</t>
+          <t>87269</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -12556,12 +12556,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>298919</t>
+          <t>302299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>356601</t>
+          <t>356264</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12571,12 +12571,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>274867</t>
+          <t>278652</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>322171</t>
+          <t>326327</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12606,12 +12606,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12626,12 +12626,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>594126</t>
+          <t>594769</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>663477</t>
+          <t>666620</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12641,12 +12641,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -12669,12 +12669,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>138459</t>
+          <t>139163</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>186916</t>
+          <t>188180</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12684,12 +12684,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12704,12 +12704,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>156194</t>
+          <t>157397</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194451</t>
+          <t>194181</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12719,12 +12719,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>307098</t>
+          <t>307184</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>365560</t>
+          <t>366133</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -12782,12 +12782,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>79679</t>
+          <t>82270</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>118683</t>
+          <t>120271</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12797,12 +12797,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12817,12 +12817,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>115952</t>
+          <t>116328</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>153248</t>
+          <t>152398</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12832,12 +12832,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12852,12 +12852,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>206505</t>
+          <t>204335</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>259211</t>
+          <t>257098</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12867,12 +12867,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -12895,12 +12895,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>21010</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>44761</t>
+          <t>42999</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12910,12 +12910,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22128</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41947</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12945,12 +12945,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12965,12 +12965,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>48086</t>
+          <t>46341</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>81690</t>
+          <t>77475</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12980,12 +12980,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -13008,12 +13008,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21221</t>
+          <t>20671</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13023,12 +13023,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13043,12 +13043,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23012</t>
+          <t>22429</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>17736</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37958</t>
+          <t>38531</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -13121,12 +13121,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51161</t>
+          <t>52247</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13136,12 +13136,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13191,12 +13191,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>10802</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>54400</t>
+          <t>60023</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -13346,17 +13346,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1502896</t>
+          <t>1502897</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1180348</t>
+          <t>1161021</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1644049</t>
+          <t>1644410</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1052924</t>
+          <t>1077244</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1396235</t>
+          <t>1394743</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13401,12 +13401,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13421,12 +13421,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2430800</t>
+          <t>2425308</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2977114</t>
+          <t>2976097</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13436,12 +13436,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,92%</t>
         </is>
       </c>
     </row>
@@ -13464,12 +13464,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>609427</t>
+          <t>622859</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>865848</t>
+          <t>863934</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13479,12 +13479,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13499,12 +13499,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>678780</t>
+          <t>696736</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>913187</t>
+          <t>912637</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13514,12 +13514,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13534,12 +13534,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1406806</t>
+          <t>1389302</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1738497</t>
+          <t>1743924</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13549,12 +13549,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>605306</t>
+          <t>604758</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1398817</t>
+          <t>1399866</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13592,12 +13592,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13612,12 +13612,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>859456</t>
+          <t>857934</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1517507</t>
+          <t>1499648</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13627,12 +13627,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13647,12 +13647,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1558532</t>
+          <t>1509839</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2567027</t>
+          <t>2572100</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13662,12 +13662,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -13690,12 +13690,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>139762</t>
+          <t>136979</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>209841</t>
+          <t>206601</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13725,12 +13725,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>205942</t>
+          <t>209030</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>289651</t>
+          <t>291926</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13760,12 +13760,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>372841</t>
+          <t>378913</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>482389</t>
+          <t>483327</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -13803,12 +13803,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>71023</t>
+          <t>71091</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>118811</t>
+          <t>119182</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>123533</t>
+          <t>124329</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>176933</t>
+          <t>179558</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13873,12 +13873,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>212524</t>
+          <t>210126</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>280430</t>
+          <t>283116</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -13916,12 +13916,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>50771</t>
+          <t>49431</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>99602</t>
+          <t>102096</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13931,12 +13931,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>51053</t>
+          <t>51779</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>81630</t>
+          <t>81388</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13986,12 +13986,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>108805</t>
+          <t>109554</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>167499</t>
+          <t>168465</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1203-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1203-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>388043</t>
+          <t>386620</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>451908</t>
+          <t>450275</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>405740</t>
+          <t>407687</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>473393</t>
+          <t>476941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>813511</t>
+          <t>815973</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>901347</t>
+          <t>910925</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,82%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250892</t>
+          <t>250075</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308640</t>
+          <t>306655</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>329517</t>
+          <t>327442</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>397513</t>
+          <t>394329</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>597772</t>
+          <t>596016</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>682645</t>
+          <t>684219</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>216453</t>
+          <t>216132</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>269741</t>
+          <t>273534</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>328281</t>
+          <t>331558</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>393642</t>
+          <t>396674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>562818</t>
+          <t>563883</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>644913</t>
+          <t>648486</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55625</t>
+          <t>55984</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89109</t>
+          <t>86700</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85250</t>
+          <t>85108</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126664</t>
+          <t>125375</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>147589</t>
+          <t>149955</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>196990</t>
+          <t>201041</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24431</t>
+          <t>25062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17519</t>
+          <t>17084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36424</t>
+          <t>37048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29925</t>
+          <t>29635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55399</t>
+          <t>54431</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15924</t>
+          <t>15982</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14200</t>
+          <t>14636</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34426</t>
+          <t>34352</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20792</t>
+          <t>20988</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>43426</t>
+          <t>45536</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1040759</t>
+          <t>1041973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1119158</t>
+          <t>1120008</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>772436</t>
+          <t>771767</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>851674</t>
+          <t>850732</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1838775</t>
+          <t>1835459</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1947918</t>
+          <t>1947128</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,34%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>331110</t>
+          <t>327577</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>398482</t>
+          <t>398568</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>354257</t>
+          <t>354119</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>423209</t>
+          <t>425868</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>705529</t>
+          <t>704626</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>799432</t>
+          <t>801265</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164243</t>
+          <t>166464</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>217980</t>
+          <t>215602</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>253796</t>
+          <t>257965</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>317372</t>
+          <t>318632</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>433910</t>
+          <t>436749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>514535</t>
+          <t>518154</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28134</t>
+          <t>27534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54049</t>
+          <t>54380</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47340</t>
+          <t>47229</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77661</t>
+          <t>76156</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80958</t>
+          <t>81195</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119391</t>
+          <t>122454</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20627</t>
+          <t>20869</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33565</t>
+          <t>31809</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23291</t>
+          <t>23563</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>47262</t>
+          <t>48061</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12582</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31336</t>
+          <t>30483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17346</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38242</t>
+          <t>37377</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>313544</t>
+          <t>314999</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>361728</t>
+          <t>361594</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>227404</t>
+          <t>224705</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>271149</t>
+          <t>270096</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>554592</t>
+          <t>552871</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>621916</t>
+          <t>617181</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,05%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>114628</t>
+          <t>114513</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>155175</t>
+          <t>155188</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>90384</t>
+          <t>89360</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>128385</t>
+          <t>126794</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>212745</t>
+          <t>214367</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>269449</t>
+          <t>271312</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50335</t>
+          <t>50921</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81855</t>
+          <t>80803</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71888</t>
+          <t>72854</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106954</t>
+          <t>105940</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132019</t>
+          <t>131365</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>178533</t>
+          <t>179541</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>15080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9013</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24181</t>
+          <t>23834</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33583</t>
+          <t>35353</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13549</t>
+          <t>13333</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27446</t>
+          <t>27245</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>12695</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15028</t>
+          <t>15988</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1775778</t>
+          <t>1778128</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1893391</t>
+          <t>1893172</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1439781</t>
+          <t>1446135</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1558026</t>
+          <t>1561728</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3259736</t>
+          <t>3257929</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3418525</t>
+          <t>3422647</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,42%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>730931</t>
+          <t>727924</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>826305</t>
+          <t>823552</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>805306</t>
+          <t>804214</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>907730</t>
+          <t>906666</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1560079</t>
+          <t>1568550</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1704275</t>
+          <t>1704169</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>458331</t>
+          <t>457011</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>540597</t>
+          <t>540212</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>689229</t>
+          <t>689756</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>789759</t>
+          <t>782001</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1169856</t>
+          <t>1168883</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1294474</t>
+          <t>1296978</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>94977</t>
+          <t>96862</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>137997</t>
+          <t>138918</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>156976</t>
+          <t>153780</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208110</t>
+          <t>205116</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>263469</t>
+          <t>261413</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>325748</t>
+          <t>331787</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21930</t>
+          <t>22306</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45855</t>
+          <t>46488</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>45544</t>
+          <t>46049</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>76331</t>
+          <t>78628</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>73704</t>
+          <t>74427</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>111470</t>
+          <t>113145</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27030</t>
+          <t>26821</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>34341</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>64918</t>
+          <t>63188</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>48627</t>
+          <t>50926</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>82887</t>
+          <t>86192</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>277085</t>
+          <t>275353</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>333707</t>
+          <t>332884</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>274632</t>
+          <t>274526</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>340464</t>
+          <t>341322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>568705</t>
+          <t>569490</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>661129</t>
+          <t>656290</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274617</t>
+          <t>277107</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>335240</t>
+          <t>334126</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>341409</t>
+          <t>344234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>407617</t>
+          <t>409213</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>634808</t>
+          <t>633480</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>724130</t>
+          <t>727312</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>201274</t>
+          <t>201397</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>257427</t>
+          <t>254256</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>368970</t>
+          <t>370186</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>437679</t>
+          <t>438937</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>589654</t>
+          <t>588856</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>676104</t>
+          <t>675642</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53006</t>
+          <t>54153</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86525</t>
+          <t>85852</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>116167</t>
+          <t>116175</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>161062</t>
+          <t>157902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178199</t>
+          <t>177998</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>234122</t>
+          <t>235330</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33290</t>
+          <t>34378</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61894</t>
+          <t>61665</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55554</t>
+          <t>55354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88905</t>
+          <t>91216</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97227</t>
+          <t>97739</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141349</t>
+          <t>140218</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11564</t>
+          <t>12004</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30612</t>
+          <t>30167</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31774</t>
+          <t>31494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59559</t>
+          <t>57529</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>49368</t>
+          <t>49728</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>81829</t>
+          <t>81324</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>894999</t>
+          <t>894983</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>980599</t>
+          <t>983130</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>621505</t>
+          <t>625043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>708571</t>
+          <t>709172</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1538544</t>
+          <t>1544881</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1671411</t>
+          <t>1670991</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,98%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>509190</t>
+          <t>506852</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>591952</t>
+          <t>588075</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>452791</t>
+          <t>457078</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>530203</t>
+          <t>533981</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>987820</t>
+          <t>985690</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1101045</t>
+          <t>1097864</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>317890</t>
+          <t>316441</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>385717</t>
+          <t>388119</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>367401</t>
+          <t>368139</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>443696</t>
+          <t>442094</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>706297</t>
+          <t>708977</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>807209</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57035</t>
+          <t>57390</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92826</t>
+          <t>92822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75266</t>
+          <t>72946</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114412</t>
+          <t>113349</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>139922</t>
+          <t>140749</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192353</t>
+          <t>194088</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25727</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53426</t>
+          <t>52916</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>53497</t>
+          <t>54349</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87079</t>
+          <t>85944</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>85513</t>
+          <t>85533</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>127719</t>
+          <t>128577</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>21886</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41963</t>
+          <t>43772</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31012</t>
+          <t>30220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57486</t>
+          <t>57958</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>222715</t>
+          <t>220615</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>266855</t>
+          <t>266802</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>169420</t>
+          <t>170299</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>215889</t>
+          <t>214776</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>404607</t>
+          <t>407189</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>468611</t>
+          <t>469054</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,02%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>131259</t>
+          <t>130455</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>173395</t>
+          <t>172428</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>129043</t>
+          <t>130716</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>171403</t>
+          <t>174643</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>274706</t>
+          <t>271202</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>333904</t>
+          <t>333075</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>51704</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>86749</t>
+          <t>86315</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68602</t>
+          <t>68964</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103801</t>
+          <t>107148</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>131447</t>
+          <t>130929</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>178761</t>
+          <t>180174</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22354</t>
+          <t>20685</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25522</t>
+          <t>24322</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6123,47 +6123,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>25898</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>16649</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>39506</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>1,78%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>25898</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>15665</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>39272</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>11958</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24555</t>
+          <t>24766</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9971</t>
+          <t>10954</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31606</t>
+          <t>31825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1431466</t>
+          <t>1427916</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1550622</t>
+          <t>1549675</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1099926</t>
+          <t>1111177</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1214254</t>
+          <t>1225619</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2573573</t>
+          <t>2572167</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2735004</t>
+          <t>2732454</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>951912</t>
+          <t>952536</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1058516</t>
+          <t>1059265</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>967806</t>
+          <t>963251</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1078416</t>
+          <t>1072784</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1942953</t>
+          <t>1943444</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2105724</t>
+          <t>2099044</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>597121</t>
+          <t>599748</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>694742</t>
+          <t>695082</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>844265</t>
+          <t>849226</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>951940</t>
+          <t>955246</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1470620</t>
+          <t>1475548</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1614476</t>
+          <t>1614164</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>127647</t>
+          <t>129692</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>177859</t>
+          <t>179762</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>214725</t>
+          <t>212999</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>277316</t>
+          <t>276482</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>359287</t>
+          <t>357026</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>439846</t>
+          <t>440530</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>70424</t>
+          <t>70956</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>110790</t>
+          <t>110094</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>129303</t>
+          <t>131246</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>180923</t>
+          <t>181424</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>211673</t>
+          <t>213712</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>276762</t>
+          <t>278238</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22648</t>
+          <t>23035</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>45749</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>56786</t>
+          <t>56021</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>93339</t>
+          <t>91150</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>87584</t>
+          <t>87312</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>131028</t>
+          <t>130934</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>202146</t>
+          <t>203495</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>252088</t>
+          <t>252855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>186849</t>
+          <t>189103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>241062</t>
+          <t>242370</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>402346</t>
+          <t>404797</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>476396</t>
+          <t>479315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197314</t>
+          <t>197631</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246833</t>
+          <t>246249</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239059</t>
+          <t>242803</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297351</t>
+          <t>299657</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>450155</t>
+          <t>452766</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>527822</t>
+          <t>527893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -7781,12 +7781,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>180671</t>
+          <t>182630</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>227538</t>
+          <t>230536</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>269976</t>
+          <t>269463</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>330231</t>
+          <t>327417</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>460979</t>
+          <t>464497</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>543041</t>
+          <t>538550</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46617</t>
+          <t>47268</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75278</t>
+          <t>73968</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87965</t>
+          <t>89189</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127688</t>
+          <t>130903</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142386</t>
+          <t>141123</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>191716</t>
+          <t>191475</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37892</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53130</t>
+          <t>53528</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87419</t>
+          <t>89798</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76641</t>
+          <t>76440</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>116662</t>
+          <t>117187</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24051</t>
+          <t>23441</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25679</t>
+          <t>24436</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51710</t>
+          <t>51805</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38201</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>67749</t>
+          <t>67905</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>827153</t>
+          <t>827672</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>921967</t>
+          <t>920563</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>658338</t>
+          <t>660718</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>745716</t>
+          <t>743782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1507894</t>
+          <t>1510100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1643599</t>
+          <t>1636841</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,35%</t>
         </is>
       </c>
     </row>
@@ -8463,12 +8463,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>657497</t>
+          <t>656735</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>742294</t>
+          <t>746952</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>618248</t>
+          <t>614643</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>702318</t>
+          <t>699774</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1294161</t>
+          <t>1304602</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1422103</t>
+          <t>1419305</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>344124</t>
+          <t>342944</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>413078</t>
+          <t>415874</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>412108</t>
+          <t>412174</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>485533</t>
+          <t>493828</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>773513</t>
+          <t>774884</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>882989</t>
+          <t>881990</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49388</t>
+          <t>48893</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82966</t>
+          <t>80419</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80131</t>
+          <t>80303</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>120254</t>
+          <t>123092</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8739,47 +8739,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>6,2%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>164040</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>138354</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>191288</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>4,04%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>164040</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>140991</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>192957</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17265</t>
+          <t>17335</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38289</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39020</t>
+          <t>38500</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>68373</t>
+          <t>69172</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>62257</t>
+          <t>63929</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>98186</t>
+          <t>99197</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -8915,12 +8915,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19197</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42044</t>
+          <t>42267</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15818</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36380</t>
+          <t>36076</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39862</t>
+          <t>39787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68779</t>
+          <t>71151</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>231323</t>
+          <t>229538</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>278756</t>
+          <t>279304</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9160,12 +9160,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>193389</t>
+          <t>193196</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>239410</t>
+          <t>242875</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>441952</t>
+          <t>438860</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>508733</t>
+          <t>506777</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,28%</t>
         </is>
       </c>
     </row>
@@ -9258,12 +9258,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>157243</t>
+          <t>161155</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>204320</t>
+          <t>208372</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>174321</t>
+          <t>171315</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>218608</t>
+          <t>218261</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>346870</t>
+          <t>343264</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>409573</t>
+          <t>409741</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64972</t>
+          <t>63867</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101355</t>
+          <t>100440</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>95299</t>
+          <t>95262</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>133521</t>
+          <t>134642</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>170200</t>
+          <t>167610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>222268</t>
+          <t>219018</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>30573</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21110</t>
+          <t>21777</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9534,47 +9534,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>29830</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>20287</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>42211</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
           <t>3,85%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>29830</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>19769</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>43210</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14720</t>
+          <t>13705</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14546</t>
+          <t>14572</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7019</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>22849</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11512</t>
+          <t>11432</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18194</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -9940,12 +9940,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1294187</t>
+          <t>1301635</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1414321</t>
+          <t>1417557</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1077794</t>
+          <t>1079062</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1186028</t>
+          <t>1195681</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9990,12 +9990,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2408390</t>
+          <t>2402806</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2558235</t>
+          <t>2557337</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1053044</t>
+          <t>1055355</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1162536</t>
+          <t>1160576</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1065818</t>
+          <t>1058090</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1181744</t>
+          <t>1178251</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2148587</t>
+          <t>2148424</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2301504</t>
+          <t>2307001</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>620044</t>
+          <t>614743</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>714419</t>
+          <t>709469</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>808393</t>
+          <t>802119</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>913163</t>
+          <t>910666</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10216,12 +10216,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1455015</t>
+          <t>1454269</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1589357</t>
+          <t>1598705</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>120627</t>
+          <t>119730</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>166529</t>
+          <t>165886</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>188441</t>
+          <t>188501</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>247369</t>
+          <t>248540</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>317735</t>
+          <t>325442</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>399597</t>
+          <t>399558</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>45175</t>
+          <t>45921</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>75723</t>
+          <t>77432</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>105919</t>
+          <t>107461</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>151626</t>
+          <t>151873</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>160601</t>
+          <t>159449</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>215586</t>
+          <t>216384</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -10505,12 +10505,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>35581</t>
+          <t>35954</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63923</t>
+          <t>65531</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10540,12 +10540,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>51172</t>
+          <t>50900</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>84551</t>
+          <t>84344</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>95774</t>
+          <t>94456</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>140322</t>
+          <t>138611</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -10961,32 +10961,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>183165</t>
+          <t>207181</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>164546</t>
+          <t>184248</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>204435</t>
+          <t>229535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10996,32 +10996,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>161755</t>
+          <t>173815</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145167</t>
+          <t>156525</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181228</t>
+          <t>193686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11031,32 +11031,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>344920</t>
+          <t>380996</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>320041</t>
+          <t>351264</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>375395</t>
+          <t>412385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -11074,32 +11074,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>107367</t>
+          <t>128315</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92024</t>
+          <t>108424</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125595</t>
+          <t>150109</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11109,32 +11109,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>170389</t>
+          <t>185735</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152771</t>
+          <t>166735</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186594</t>
+          <t>202974</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11144,32 +11144,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>277756</t>
+          <t>314050</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>253526</t>
+          <t>288300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>301957</t>
+          <t>342108</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -11187,32 +11187,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>132281</t>
+          <t>140724</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>113547</t>
+          <t>123705</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>149688</t>
+          <t>160967</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11222,32 +11222,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>233513</t>
+          <t>248054</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>214192</t>
+          <t>229085</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>257159</t>
+          <t>267879</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11257,32 +11257,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>365794</t>
+          <t>388778</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>340530</t>
+          <t>360748</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>395456</t>
+          <t>415796</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>29,74%</t>
         </is>
       </c>
     </row>
@@ -11300,32 +11300,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43504</t>
+          <t>48979</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34297</t>
+          <t>37824</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56166</t>
+          <t>61971</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11335,67 +11335,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>97974</t>
+          <t>109525</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85464</t>
+          <t>94313</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111383</t>
+          <t>124834</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>15,22%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>158504</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>139656</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>177821</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>11,34%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>141478</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>125111</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>160827</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -11413,32 +11413,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>29388</t>
+          <t>32559</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20053</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39731</t>
+          <t>43906</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11448,32 +11448,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>64339</t>
+          <t>72799</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53432</t>
+          <t>61403</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77946</t>
+          <t>86652</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11483,32 +11483,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>93727</t>
+          <t>105359</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78476</t>
+          <t>89000</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>111219</t>
+          <t>123925</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -11526,32 +11526,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18761</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27870</t>
+          <t>30644</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11561,32 +11561,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25574</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19192</t>
+          <t>22452</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33344</t>
+          <t>38500</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11596,32 +11596,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>44335</t>
+          <t>50448</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35363</t>
+          <t>39920</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>56663</t>
+          <t>63751</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -11639,17 +11639,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>514467</t>
+          <t>578052</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>514467</t>
+          <t>578052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>514467</t>
+          <t>578052</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11674,17 +11674,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>753544</t>
+          <t>820083</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>753544</t>
+          <t>820083</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>753544</t>
+          <t>820083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11709,17 +11709,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1268011</t>
+          <t>1398135</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1268011</t>
+          <t>1398135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1268011</t>
+          <t>1398135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11756,32 +11756,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>989634</t>
+          <t>1050868</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>662706</t>
+          <t>998324</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1123807</t>
+          <t>1115876</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11791,32 +11791,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>817413</t>
+          <t>874788</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>600802</t>
+          <t>831628</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>934657</t>
+          <t>916601</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11826,32 +11826,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1807046</t>
+          <t>1925656</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1437896</t>
+          <t>1854330</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2025883</t>
+          <t>1992140</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -11869,32 +11869,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>515451</t>
+          <t>573416</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>361026</t>
+          <t>527274</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>597365</t>
+          <t>622777</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11904,32 +11904,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>493678</t>
+          <t>560723</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>368119</t>
+          <t>523677</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>564753</t>
+          <t>598279</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11939,32 +11939,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1009129</t>
+          <t>1134139</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>809017</t>
+          <t>1072561</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128892</t>
+          <t>1196489</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -11982,32 +11982,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>593049</t>
+          <t>390255</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>377536</t>
+          <t>354445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1130126</t>
+          <t>428083</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12017,32 +12017,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>686882</t>
+          <t>464096</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>484127</t>
+          <t>429768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1102413</t>
+          <t>498626</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12052,32 +12052,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1279931</t>
+          <t>854351</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>914677</t>
+          <t>807938</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1942511</t>
+          <t>907918</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -12095,32 +12095,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>103300</t>
+          <t>112423</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71615</t>
+          <t>91044</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127826</t>
+          <t>133130</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12130,32 +12130,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>129215</t>
+          <t>144099</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96496</t>
+          <t>125815</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154601</t>
+          <t>167781</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12165,32 +12165,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>232516</t>
+          <t>256523</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>186333</t>
+          <t>229789</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>270488</t>
+          <t>289413</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -12208,32 +12208,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53145</t>
+          <t>65067</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34885</t>
+          <t>47926</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>75497</t>
+          <t>85685</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12243,32 +12243,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73580</t>
+          <t>83243</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54006</t>
+          <t>68159</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93538</t>
+          <t>99976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12278,32 +12278,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>126725</t>
+          <t>148310</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>101057</t>
+          <t>126940</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>155233</t>
+          <t>177079</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -12321,32 +12321,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32813</t>
+          <t>35181</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>25205</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47449</t>
+          <t>48784</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12356,32 +12356,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>35514</t>
+          <t>42860</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>31754</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49934</t>
+          <t>57240</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12391,32 +12391,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>68327</t>
+          <t>78041</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50483</t>
+          <t>62224</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87269</t>
+          <t>97319</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -12434,17 +12434,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2287392</t>
+          <t>2227210</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2287392</t>
+          <t>2227210</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2287392</t>
+          <t>2227210</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12469,17 +12469,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2236282</t>
+          <t>2169811</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2236282</t>
+          <t>2169811</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2236282</t>
+          <t>2169811</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12504,17 +12504,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4523674</t>
+          <t>4397020</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4523674</t>
+          <t>4397020</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4523674</t>
+          <t>4397020</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12551,32 +12551,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>330097</t>
+          <t>357478</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>302299</t>
+          <t>327217</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>356264</t>
+          <t>388146</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12586,32 +12586,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>301003</t>
+          <t>330346</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>278652</t>
+          <t>305988</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>326327</t>
+          <t>355361</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12621,32 +12621,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>631100</t>
+          <t>687825</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>594769</t>
+          <t>652001</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>666620</t>
+          <t>728624</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -12664,32 +12664,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>160582</t>
+          <t>186950</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>139163</t>
+          <t>164476</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>188180</t>
+          <t>213349</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12699,32 +12699,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>174950</t>
+          <t>192251</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>157397</t>
+          <t>172190</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194181</t>
+          <t>214644</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12734,32 +12734,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>335532</t>
+          <t>379201</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>307184</t>
+          <t>343829</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>366133</t>
+          <t>411450</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -12777,32 +12777,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>110350</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>82270</t>
+          <t>93315</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>120271</t>
+          <t>132447</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12812,32 +12812,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>133028</t>
+          <t>149831</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116328</t>
+          <t>130451</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>152398</t>
+          <t>168842</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12847,32 +12847,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>230650</t>
+          <t>260180</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>204335</t>
+          <t>235525</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>257098</t>
+          <t>291812</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -12890,32 +12890,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30325</t>
+          <t>35528</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21010</t>
+          <t>24054</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42999</t>
+          <t>49015</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12925,32 +12925,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30476</t>
+          <t>36809</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21769</t>
+          <t>27469</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42589</t>
+          <t>50033</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12960,32 +12960,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>60801</t>
+          <t>72336</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46341</t>
+          <t>56763</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>77475</t>
+          <t>89709</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -13003,27 +13003,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20671</t>
+          <t>22747</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -13038,32 +13038,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>17177</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22429</t>
+          <t>26494</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13073,32 +13073,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>26723</t>
+          <t>29700</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17736</t>
+          <t>20730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38531</t>
+          <t>41861</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -13116,32 +13116,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>16268</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52247</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13151,32 +13151,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>13997</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13186,32 +13186,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>22280</t>
+          <t>17222</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10802</t>
+          <t>10397</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>60023</t>
+          <t>25694</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -13229,17 +13229,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13264,17 +13264,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13299,17 +13299,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13346,32 +13346,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1502897</t>
+          <t>1615527</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1161021</t>
+          <t>1547227</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1644410</t>
+          <t>1682878</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13381,32 +13381,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1280170</t>
+          <t>1378950</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1077244</t>
+          <t>1328678</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1394743</t>
+          <t>1435408</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13416,32 +13416,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2783066</t>
+          <t>2994477</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2425308</t>
+          <t>2900930</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2976097</t>
+          <t>3081443</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -13459,32 +13459,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>783399</t>
+          <t>888681</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>622859</t>
+          <t>831851</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>863934</t>
+          <t>950990</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13494,32 +13494,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>839018</t>
+          <t>938709</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>696736</t>
+          <t>890960</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>912637</t>
+          <t>986207</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13529,32 +13529,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1622417</t>
+          <t>1827390</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1389302</t>
+          <t>1755861</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1743924</t>
+          <t>1906735</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -13572,32 +13572,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>822952</t>
+          <t>641328</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>604758</t>
+          <t>594468</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1399866</t>
+          <t>689159</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13607,32 +13607,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1053423</t>
+          <t>861981</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>857934</t>
+          <t>815580</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1499648</t>
+          <t>906773</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13642,32 +13642,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1876375</t>
+          <t>1503309</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1509839</t>
+          <t>1440957</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2572100</t>
+          <t>1570584</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -13685,32 +13685,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>177129</t>
+          <t>196930</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>136979</t>
+          <t>168982</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>206601</t>
+          <t>225548</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13720,32 +13720,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>257666</t>
+          <t>290433</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>209030</t>
+          <t>261712</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>291926</t>
+          <t>318567</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13755,32 +13755,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>434795</t>
+          <t>487363</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>378913</t>
+          <t>448677</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>483327</t>
+          <t>526724</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -13798,32 +13798,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>94264</t>
+          <t>110150</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>71091</t>
+          <t>87642</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>119182</t>
+          <t>134567</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13833,32 +13833,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>152912</t>
+          <t>173220</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>124329</t>
+          <t>152873</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>179558</t>
+          <t>195070</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13868,32 +13868,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>247175</t>
+          <t>283369</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>210126</t>
+          <t>252398</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>283116</t>
+          <t>317088</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -13911,22 +13911,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>67841</t>
+          <t>64233</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>49431</t>
+          <t>50452</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>102096</t>
+          <t>82224</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13946,32 +13946,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>67101</t>
+          <t>81478</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>51779</t>
+          <t>68243</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>81388</t>
+          <t>98784</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13981,32 +13981,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>134942</t>
+          <t>145711</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>109554</t>
+          <t>125955</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>168465</t>
+          <t>169519</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -14024,17 +14024,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3448482</t>
+          <t>3516849</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3448482</t>
+          <t>3516849</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3448482</t>
+          <t>3516849</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14059,17 +14059,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3650289</t>
+          <t>3724771</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3650289</t>
+          <t>3724771</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3650289</t>
+          <t>3724771</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14094,17 +14094,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>7098771</t>
+          <t>7241620</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7098771</t>
+          <t>7241620</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7098771</t>
+          <t>7241620</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
